--- a/e2e/excel/VALID.xlsx
+++ b/e2e/excel/VALID.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="27945" windowHeight="12795"/>
+    <workbookView windowWidth="27945" windowHeight="13395"/>
   </bookViews>
   <sheets>
     <sheet name="Phiếu chấm điểm" sheetId="1" r:id="rId1"/>
@@ -116,7 +116,7 @@
     <t>A11</t>
   </si>
   <si>
-    <t>A12</t>
+    <t>A99</t>
   </si>
   <si>
     <t>A13</t>
